--- a/branches/fix/go-publish-bootstrap/StructureDefinition-mii-ex-biobank-infektiositaetsstatus.xlsx
+++ b/branches/fix/go-publish-bootstrap/StructureDefinition-mii-ex-biobank-infektiositaetsstatus.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T12:26:45+00:00</t>
+    <t>2026-09-09T12:40:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/fix/go-publish-bootstrap/StructureDefinition-mii-ex-biobank-infektiositaetsstatus.xlsx
+++ b/branches/fix/go-publish-bootstrap/StructureDefinition-mii-ex-biobank-infektiositaetsstatus.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T12:40:12+00:00</t>
+    <t>2026-09-09T12:51:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/fix/go-publish-bootstrap/StructureDefinition-mii-ex-biobank-infektiositaetsstatus.xlsx
+++ b/branches/fix/go-publish-bootstrap/StructureDefinition-mii-ex-biobank-infektiositaetsstatus.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T12:51:05+00:00</t>
+    <t>2026-09-09T12:56:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/fix/go-publish-bootstrap/StructureDefinition-mii-ex-biobank-infektiositaetsstatus.xlsx
+++ b/branches/fix/go-publish-bootstrap/StructureDefinition-mii-ex-biobank-infektiositaetsstatus.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T12:56:34+00:00</t>
+    <t>2026-09-09T13:08:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/fix/go-publish-bootstrap/StructureDefinition-mii-ex-biobank-infektiositaetsstatus.xlsx
+++ b/branches/fix/go-publish-bootstrap/StructureDefinition-mii-ex-biobank-infektiositaetsstatus.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T13:08:30+00:00</t>
+    <t>2026-09-09T13:18:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/fix/go-publish-bootstrap/StructureDefinition-mii-ex-biobank-infektiositaetsstatus.xlsx
+++ b/branches/fix/go-publish-bootstrap/StructureDefinition-mii-ex-biobank-infektiositaetsstatus.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T13:18:24+00:00</t>
+    <t>2026-09-09T13:33:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/fix/go-publish-bootstrap/StructureDefinition-mii-ex-biobank-infektiositaetsstatus.xlsx
+++ b/branches/fix/go-publish-bootstrap/StructureDefinition-mii-ex-biobank-infektiositaetsstatus.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T13:33:26+00:00</t>
+    <t>2026-09-09T13:48:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/fix/go-publish-bootstrap/StructureDefinition-mii-ex-biobank-infektiositaetsstatus.xlsx
+++ b/branches/fix/go-publish-bootstrap/StructureDefinition-mii-ex-biobank-infektiositaetsstatus.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc2</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Infektiositätsstatus</t>
+    <t>MII EX Biobank Infektiositätsstatus</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T13:48:19+00:00</t>
+    <t>2026-09-11T10:07:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -341,7 +341,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-biobank/ValueSet/mii-vs-biobank-biosafety-level</t>
+    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-biobank/ValueSet/mii-vs-biobank-biosafety-level-snomedct</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
@@ -698,7 +698,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="85.2265625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="93.546875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/branches/fix/go-publish-bootstrap/StructureDefinition-mii-ex-biobank-infektiositaetsstatus.xlsx
+++ b/branches/fix/go-publish-bootstrap/StructureDefinition-mii-ex-biobank-infektiositaetsstatus.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T10:07:49+00:00</t>
+    <t>2026-09-11T10:33:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
